--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_prism_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_prism_data.xlsx
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.33x1.10</t>
+          <t>1.05x1.35</t>
         </is>
       </c>
       <c r="J2" t="n">

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_prism_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_prism_data.xlsx
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.05x1.35</t>
+          <t>1.30x1.35</t>
         </is>
       </c>
       <c r="J2" t="n">
